--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK92"/>
+  <dimension ref="A1:AK100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45954.375</v>
+        <v>45954.35763888889</v>
       </c>
     </row>
     <row r="9">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45954.41666666666</v>
+        <v>45954.375</v>
       </c>
     </row>
     <row r="11">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.41666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="21">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45954.48958333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45954.5</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="26">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.48958333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.5</v>
       </c>
     </row>
     <row r="28">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="31">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="54">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45954.63541666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,16 +9480,16 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.63541666666</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="74">
@@ -9916,27 +9916,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="77">
@@ -10303,27 +10303,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="79">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="M79" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N79" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,11 +10641,11 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z79" t="n">
         <v>2</v>
       </c>
-      <c r="Z79" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AA79" t="n">
         <v>0</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="80">
@@ -10690,27 +10690,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="81">
@@ -10819,27 +10819,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="82">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10992,10 +10992,10 @@
         <v>2.95</v>
       </c>
       <c r="M82" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11022,16 +11022,16 @@
         <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="83">
@@ -11077,27 +11077,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="84">
@@ -11206,27 +11206,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="85">
@@ -11335,27 +11335,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="86">
@@ -11464,27 +11464,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="87">
@@ -11593,27 +11593,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="88">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11796,16 +11796,16 @@
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="89">
@@ -11851,27 +11851,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45954.8125</v>
+        <v>45954.70833333334</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45954.89930555555</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="92">
@@ -12238,126 +12238,1158 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>07 Vestur</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>EB - Streymur</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>B36</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Suduroy</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>B68</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NSÍ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>KÍ</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK95" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Wisła Płock</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3" t="n">
+        <v>45954.8125</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3" t="n">
+        <v>45954.89930555555</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>New Mexico United</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Rhode Island</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="inlineStr">
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK92" s="3" t="n">
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK100"/>
+  <dimension ref="A1:AK102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45954.41666666666</v>
+        <v>45954.39583333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45954.41666666666</v>
+        <v>45954.39583333334</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.41666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.41666666666</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="23">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45954.48958333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45954.5</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.48958333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.5</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="33">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="44">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="48">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="53">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="56">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45954.63541666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.63541666666</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="80">
@@ -10690,27 +10690,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="81">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11335,12 +11335,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="86">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="87">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="M88" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11796,16 +11796,16 @@
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="90">
@@ -11980,27 +11980,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45954.70833333334</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="91">
@@ -12109,27 +12109,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,16 +12183,16 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.70833333334</v>
       </c>
     </row>
     <row r="93">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45954.8125</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="99">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45954.89930555555</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="100">
@@ -13270,126 +13270,384 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3" t="n">
+        <v>45954.8125</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3" t="n">
+        <v>45954.89930555555</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>New Mexico United</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Rhode Island</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="inlineStr">
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK100" s="3" t="n">
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N3" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,16 +10125,16 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12054,16 +12054,16 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,16 +12183,16 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G99" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="46">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="50">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="58">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,16 +10125,16 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.95</v>
+        <v>1.3</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="N81" t="n">
-        <v>2.35</v>
+        <v>10</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G99" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK102"/>
+  <dimension ref="A1:AK115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.41666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="24">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45954.48958333334</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,10 +4185,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45954.5</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.48958333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.5</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="38">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="56">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="M60" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="65">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="68">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45954.63541666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="79">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="80">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="81">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="82">
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="83">
@@ -11077,27 +11077,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="84">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="85">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="86">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="87">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.63541666666</v>
       </c>
     </row>
     <row r="88">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12054,16 +12054,16 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,27 +12238,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45954.70833333334</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="96">
@@ -12754,27 +12754,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="97">
@@ -12883,27 +12883,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="99">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="100">
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45954.8125</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="101">
@@ -13399,27 +13399,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45954.89930555555</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="102">
@@ -13528,126 +13528,1803 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3" t="n">
+        <v>45954.66666666666</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M103" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N103" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X103" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK103" s="3" t="n">
+        <v>45954.67708333334</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Spain Primera Division RFEF Group 2</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Barakaldo CF</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>CD Tenerife</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK104" s="3" t="n">
+        <v>45954.67708333334</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M105" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N105" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK105" s="3" t="n">
+        <v>45954.70833333334</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK106" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Víkingur</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK107" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Wisła Płock</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK108" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>07 Vestur</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>EB - Streymur</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>B68</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK110" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>NSÍ</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>KÍ</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>B36</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Suduroy</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" s="3" t="n">
+        <v>45954.8125</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK114" s="3" t="n">
+        <v>45954.89930555555</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>New Mexico United</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Rhode Island</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="inlineStr">
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK102" s="3" t="n">
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK115" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK115"/>
+  <dimension ref="A1:AK125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45954.39583333334</v>
+        <v>45954.375</v>
       </c>
     </row>
     <row r="12">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45954.41666666666</v>
+        <v>45954.39583333334</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.41666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.41666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,10 +4185,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45954.48958333334</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45954.5</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.47916666666</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.47916666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.48958333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.5</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="44">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7244,17 +7244,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="61">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="64">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N65" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="66">
@@ -8884,27 +8884,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="74">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45954.63541666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="88">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="94">
@@ -12496,27 +12496,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="95">
@@ -12625,27 +12625,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.63541666666</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z98" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="100">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="101">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="102">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.95</v>
+        <v>1.3</v>
       </c>
       <c r="M103" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="N103" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13731,16 +13731,16 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="104">
@@ -13786,27 +13786,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="105">
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45954.70833333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="106">
@@ -14044,27 +14044,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="107">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="108">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="109">
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="110">
@@ -14560,27 +14560,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="111">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="112">
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="113">
@@ -14947,27 +14947,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15021,16 +15021,16 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45954.8125</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45954.89930555555</v>
+        <v>45954.70833333334</v>
       </c>
     </row>
     <row r="115">
@@ -15205,126 +15205,1416 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Wisła Płock</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK115" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Víkingur</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>B36</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Suduroy</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK117" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>07 Vestur</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>EB - Streymur</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK118" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK119" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>NSÍ</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>KÍ</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK120" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>B68</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK121" s="3" t="n">
+        <v>45954.79166666666</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK122" s="3" t="n">
+        <v>45954.8125</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK123" s="3" t="n">
+        <v>45954.8125</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK124" s="3" t="n">
+        <v>45954.89930555555</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>New Mexico United</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Rhode Island</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="inlineStr">
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK115" s="3" t="n">
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1359,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4056,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T37" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.28</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="M38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T38" t="n">
         <v>3.28</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8196,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.15</v>
+        <v>1.83</v>
       </c>
       <c r="M71" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="M73" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N73" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,16 +12834,16 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="M103" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="M106" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z106" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15021,16 +15021,16 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G123" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1359,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4056,16 +4056,16 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O37" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P37" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R37" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S37" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S38" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T38" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.28</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8196,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="M78" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="N78" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="M86" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N86" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="M88" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,61 +11892,61 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
@@ -11959,10 +11959,10 @@
         </is>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,16 +12834,16 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,49 +13698,49 @@
         </is>
       </c>
       <c r="L103" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M103" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N103" t="n">
+        <v>5</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z103" t="n">
         <v>2</v>
-      </c>
-      <c r="M103" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N103" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z104" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.3</v>
+        <v>2.95</v>
       </c>
       <c r="M106" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>10</v>
+        <v>2.35</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G123" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T37" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.28</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O38" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R38" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8970,10 +8970,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="M71" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N71" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.15</v>
+        <v>1.83</v>
       </c>
       <c r="M72" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N72" t="n">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N81" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,61 +11892,61 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
@@ -11959,10 +11959,10 @@
         </is>
       </c>
       <c r="AG89" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,55 +13053,55 @@
         </is>
       </c>
       <c r="L98" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M98" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N98" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z98" t="n">
         <v>2</v>
       </c>
-      <c r="M98" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N98" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" t="n">
-        <v>0</v>
-      </c>
-      <c r="W98" t="n">
-        <v>0</v>
-      </c>
-      <c r="X98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y98" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AA98" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,14 +13440,14 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N101" t="n">
         <v>3.45</v>
       </c>
-      <c r="N101" t="n">
-        <v>2.4</v>
-      </c>
       <c r="O101" t="n">
         <v>0</v>
       </c>
@@ -13479,16 +13479,16 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z101" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.65</v>
+        <v>2.95</v>
       </c>
       <c r="M103" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N103" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z103" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O37" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P37" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R37" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S37" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S38" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T38" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.28</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8196,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8970,10 +8970,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N69" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,16 +9351,16 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB69" t="n">
         <v>1.6</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="M78" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="M79" t="n">
         <v>3.65</v>
       </c>
       <c r="N79" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="M81" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M87" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,10 +12021,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M90" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N90" t="n">
         <v>4.6</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,16 +13479,16 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="M102" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>3.85</v>
+        <v>2.35</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.95</v>
+        <v>1.3</v>
       </c>
       <c r="M103" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="N103" t="n">
-        <v>2.35</v>
+        <v>10</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="M107" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Z107" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15021,16 +15021,16 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G120" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK125"/>
+  <dimension ref="A1:AK124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1359,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45954.41666666666</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45954.41666666666</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="23">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3774,52 +3774,52 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,16 +4314,16 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="35">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.47916666666</v>
       </c>
     </row>
     <row r="37">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N37" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="O37" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T37" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.28</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45954.47916666666</v>
+        <v>45954.48958333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45954.48958333334</v>
+        <v>45954.5</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45954.5</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="41">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="45">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6599,17 +6599,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="60">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8196,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8368,27 +8368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="M62" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="N62" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,16 +8448,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9357,10 +9357,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>3.53</v>
       </c>
       <c r="N70" t="n">
-        <v>2.9</v>
+        <v>3.66</v>
       </c>
       <c r="O70" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="71">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.83</v>
+        <v>2.91</v>
       </c>
       <c r="M72" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="N72" t="n">
-        <v>3.65</v>
+        <v>2.29</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="74">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="M78" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="N78" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="M79" t="n">
-        <v>3.65</v>
+        <v>3.99</v>
       </c>
       <c r="N79" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="M81" t="n">
-        <v>4.1</v>
+        <v>2.97</v>
       </c>
       <c r="N81" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.63</v>
+        <v>2.45</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="M86" t="n">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="N86" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M87" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N87" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="M90" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N90" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.63541666666</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45954.63541666666</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="96">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>3.21</v>
       </c>
       <c r="N99" t="n">
-        <v>4.3</v>
+        <v>2.29</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N100" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="102">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M106" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z106" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>2</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="109">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45954.70833333334</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.70833333334</v>
       </c>
     </row>
     <row r="116">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.8125</v>
       </c>
     </row>
     <row r="122">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45954.8125</v>
+        <v>45954.89930555555</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16486,135 +16486,6 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45954.89930555555</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1359,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45954.4375</v>
+        <v>45954.41666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.4375</v>
       </c>
     </row>
     <row r="25">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3774,52 +3774,52 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.45833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45954.47916666666</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="37">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="N37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.91</v>
       </c>
-      <c r="O37" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q37" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R37" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S37" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45954.48958333334</v>
+        <v>45954.47916666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45954.5</v>
+        <v>45954.48958333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.5</v>
       </c>
     </row>
     <row r="41">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="46">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6606,10 +6606,10 @@
         <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.21</v>
+        <v>2.17</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="N53" t="n">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="59">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8368,27 +8368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="M62" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="N62" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,16 +8448,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="63">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="M68" t="n">
-        <v>3.03</v>
+        <v>3.32</v>
       </c>
       <c r="N68" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="O68" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="71">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.91</v>
+        <v>1.78</v>
       </c>
       <c r="M72" t="n">
-        <v>2.95</v>
+        <v>3.53</v>
       </c>
       <c r="N72" t="n">
-        <v>2.29</v>
+        <v>3.66</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="74">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="M83" t="n">
-        <v>3.33</v>
+        <v>2.97</v>
       </c>
       <c r="N83" t="n">
-        <v>3.27</v>
+        <v>3.65</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45954.63541666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.63541666666</v>
       </c>
     </row>
     <row r="96">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="102">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="M104" t="n">
-        <v>3.92</v>
+        <v>5.8</v>
       </c>
       <c r="N104" t="n">
-        <v>4.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>3.85</v>
+        <v>2.35</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="M108" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>2.35</v>
+        <v>3.85</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="110">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15021,16 +15021,16 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G122" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK124"/>
+  <dimension ref="A1:AK121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>3.41</v>
       </c>
       <c r="M10" t="n">
-        <v>4.05</v>
+        <v>3.13</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.41</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>4.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.96</v>
+        <v>3.52</v>
       </c>
       <c r="M37" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="O37" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T37" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.28</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="N38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P38" t="n">
         <v>1.91</v>
       </c>
-      <c r="O38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q38" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R38" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="M46" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>3.67</v>
+        <v>2.71</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.17</v>
+        <v>3.21</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>2.71</v>
+        <v>1.99</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.17</v>
+        <v>3.31</v>
       </c>
       <c r="M53" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="N53" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="M68" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="N68" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,16 +9222,16 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9357,10 +9357,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,61 +9957,61 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>3.99</v>
       </c>
       <c r="N84" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="M88" t="n">
-        <v>3.99</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,14 +11892,14 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="M89" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N89" t="n">
         <v>3.65</v>
       </c>
-      <c r="N89" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.63541666666</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.19</v>
+        <v>2.68</v>
       </c>
       <c r="M94" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="N94" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45954.63541666666</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="96">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="M97" t="n">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>2.29</v>
+        <v>4.3</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z97" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="100">
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="101">
@@ -13399,27 +13399,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="102">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>9.300000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="108">
@@ -14302,27 +14302,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="109">
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="110">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="112">
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.95</v>
+        <v>2.02</v>
       </c>
       <c r="M112" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N112" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.70833333334</v>
       </c>
     </row>
     <row r="113">
@@ -14947,27 +14947,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45954.70833333334</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="116">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15592,12 +15592,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.8125</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.8125</v>
       </c>
     </row>
     <row r="120">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.89930555555</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,393 +16099,6 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45954.8125</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Univ. Concepción</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK122" s="3" t="n">
-        <v>45954.8125</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="3" t="n">
-        <v>45954.89930555555</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK124" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4806,52 +4806,52 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8067,10 +8067,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>3.03</v>
       </c>
       <c r="N68" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9357,10 +9357,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.91</v>
+        <v>4.88</v>
       </c>
       <c r="M71" t="n">
-        <v>2.95</v>
+        <v>4.05</v>
       </c>
       <c r="N71" t="n">
-        <v>2.29</v>
+        <v>1.59</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,61 +9957,61 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
-        <v>2.5</v>
+        <v>3.69</v>
       </c>
       <c r="O74" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>3.16</v>
       </c>
       <c r="N75" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="M79" t="n">
-        <v>3.16</v>
+        <v>2.97</v>
       </c>
       <c r="N79" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="n">
-        <v>3.29</v>
+        <v>3.99</v>
       </c>
       <c r="N82" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="M84" t="n">
-        <v>3.99</v>
+        <v>3.65</v>
       </c>
       <c r="N84" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="M89" t="n">
-        <v>2.97</v>
+        <v>3.33</v>
       </c>
       <c r="N89" t="n">
-        <v>3.65</v>
+        <v>3.27</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,61 +12150,61 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="M91" t="n">
         <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="M94" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N94" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="M95" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="N95" t="n">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="N97" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N104" t="n">
-        <v>3.85</v>
+        <v>2.35</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G117" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>3.41</v>
       </c>
       <c r="M11" t="n">
-        <v>4.05</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>1.97</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4290,52 +4290,52 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,49 +4410,49 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.85</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="N31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.88</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.75</v>
-      </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.21</v>
+        <v>1.95</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N51" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.17</v>
+        <v>3.31</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>3.89</v>
       </c>
       <c r="N52" t="n">
-        <v>2.71</v>
+        <v>1.78</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="M57" t="n">
-        <v>3.89</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8067,10 +8067,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8454,10 +8454,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="M68" t="n">
-        <v>3.03</v>
+        <v>3.32</v>
       </c>
       <c r="N68" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="O68" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.88</v>
+        <v>2.91</v>
       </c>
       <c r="M71" t="n">
-        <v>4.05</v>
+        <v>2.95</v>
       </c>
       <c r="N71" t="n">
-        <v>1.59</v>
+        <v>2.29</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.78</v>
+        <v>4.88</v>
       </c>
       <c r="M72" t="n">
-        <v>3.53</v>
+        <v>4.05</v>
       </c>
       <c r="N72" t="n">
-        <v>3.66</v>
+        <v>1.59</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.91</v>
+        <v>1.78</v>
       </c>
       <c r="M73" t="n">
-        <v>2.95</v>
+        <v>3.53</v>
       </c>
       <c r="N73" t="n">
-        <v>2.29</v>
+        <v>3.66</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="M75" t="n">
-        <v>3.16</v>
+        <v>3.33</v>
       </c>
       <c r="N75" t="n">
-        <v>2.88</v>
+        <v>3.27</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="M77" t="n">
         <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="M79" t="n">
-        <v>2.97</v>
+        <v>3.99</v>
       </c>
       <c r="N79" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="M90" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N90" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,61 +12150,61 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="M91" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="O91" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="M95" t="n">
-        <v>3.65</v>
+        <v>3.21</v>
       </c>
       <c r="N95" t="n">
-        <v>4.3</v>
+        <v>2.29</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="M98" t="n">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>2.29</v>
+        <v>4.3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z98" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>3.85</v>
+        <v>2.35</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="M103" t="n">
-        <v>3.92</v>
+        <v>5.8</v>
       </c>
       <c r="N103" t="n">
-        <v>4.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>2.35</v>
+        <v>3.85</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14634,16 +14634,16 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK121"/>
+  <dimension ref="A1:AK122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.41</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>1.97</v>
+        <v>3.58</v>
       </c>
       <c r="O11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45954.39583333334</v>
+        <v>45954.375</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45954.41666666666</v>
+        <v>45954.39583333334</v>
       </c>
     </row>
     <row r="15">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3903,52 +3903,52 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.7</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="N29" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4290,52 +4290,52 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>3.85</v>
       </c>
       <c r="M31" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>5.6</v>
+        <v>1.88</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="N37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.91</v>
       </c>
-      <c r="O37" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q37" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R37" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S37" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>3.52</v>
       </c>
       <c r="M38" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="O38" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S38" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T38" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.28</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="M51" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="N51" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,16 +7029,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.31</v>
+        <v>1.72</v>
       </c>
       <c r="M52" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="N52" t="n">
-        <v>1.78</v>
+        <v>3.67</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         <v>1.63</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.93</v>
+        <v>2.27</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="N66" t="n">
-        <v>3.55</v>
+        <v>2.65</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,16 +8964,16 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB66" t="n">
         <v>1.6</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="M68" t="n">
-        <v>3.32</v>
+        <v>3.03</v>
       </c>
       <c r="N68" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="N77" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="O77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="M86" t="n">
-        <v>2.97</v>
+        <v>3.65</v>
       </c>
       <c r="N86" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,61 +12021,61 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="M90" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N90" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z90" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="M93" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N93" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,16 +12576,16 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.68</v>
+        <v>1.8</v>
       </c>
       <c r="M95" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="N95" t="n">
-        <v>2.29</v>
+        <v>4.2</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z95" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.02</v>
+        <v>2.61</v>
       </c>
       <c r="M97" t="n">
-        <v>3.58</v>
+        <v>2.98</v>
       </c>
       <c r="N97" t="n">
-        <v>3.38</v>
+        <v>2.5</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.95</v>
+        <v>1.64</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="N101" t="n">
-        <v>2.35</v>
+        <v>4.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N104" t="n">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="106">
@@ -14044,27 +14044,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="107">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="109">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.70833333334</v>
       </c>
     </row>
     <row r="112">
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="M112" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N112" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45954.70833333334</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="113">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15592,12 +15592,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45954.8125</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="119">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45954.89930555555</v>
+        <v>45954.8125</v>
       </c>
     </row>
     <row r="121">
@@ -15979,126 +15979,255 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N121" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK121" s="3" t="n">
+        <v>45954.89930555555</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>New Mexico United</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Rhode Island</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="inlineStr">
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK121" s="3" t="n">
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK122" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK122"/>
+  <dimension ref="A1:AK115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.41</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>1.97</v>
+        <v>3.58</v>
       </c>
       <c r="O12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3903,52 +3903,52 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4290,52 +4290,52 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,14 +4410,14 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N31" t="n">
         <v>3.85</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.88</v>
-      </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.46875</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.47916666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="M33" t="n">
-        <v>3.94</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>5.4</v>
+        <v>2.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.47916666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45954.45833333334</v>
+        <v>45954.48958333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.5</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45954.46875</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45954.47916666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45954.47916666666</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45954.48958333334</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45954.5</v>
+        <v>45954.52083333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.2</v>
+        <v>1.72</v>
       </c>
       <c r="M43" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="N43" t="n">
-        <v>1.8</v>
+        <v>3.67</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45954.52083333334</v>
+        <v>45954.54166666666</v>
       </c>
     </row>
     <row r="46">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.17</v>
+        <v>3.31</v>
       </c>
       <c r="M51" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="N51" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,16 +7029,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N54" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.5625</v>
       </c>
     </row>
     <row r="56">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45954.54166666666</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="M61" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="N61" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,16 +8319,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8454,10 +8454,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45954.5625</v>
+        <v>45954.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="66">
@@ -8884,27 +8884,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.27</v>
+        <v>1.78</v>
       </c>
       <c r="M66" t="n">
-        <v>3.32</v>
+        <v>3.53</v>
       </c>
       <c r="N66" t="n">
-        <v>2.65</v>
+        <v>3.66</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,16 +8964,16 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.60416666666</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="M68" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="N68" t="n">
-        <v>2.76</v>
+        <v>4.1</v>
       </c>
       <c r="O68" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AA68" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M70" t="n">
-        <v>3.64</v>
+        <v>3.99</v>
       </c>
       <c r="N70" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45954.58333333334</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45954.60416666666</v>
+        <v>45954.625</v>
       </c>
     </row>
     <row r="74">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="M78" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="N78" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="M82" t="n">
-        <v>3.16</v>
+        <v>3.65</v>
       </c>
       <c r="N82" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="M84" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="N84" t="n">
-        <v>3.27</v>
+        <v>3.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11335,12 +11335,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,16 +11415,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.63541666666</v>
       </c>
     </row>
     <row r="86">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="M86" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N86" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="87">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="88">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="M89" t="n">
-        <v>3.29</v>
+        <v>3.58</v>
       </c>
       <c r="N89" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,16 +11931,16 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,61 +12021,61 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="M90" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="N90" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="O90" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="AG90" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45954.625</v>
+        <v>45954.64583333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,27 +12238,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="M92" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>4.97</v>
+        <v>3.53</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45954.63541666666</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="M93" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Z93" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="94">
@@ -12496,27 +12496,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,16 +12576,16 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.61</v>
+        <v>1.64</v>
       </c>
       <c r="M97" t="n">
-        <v>2.98</v>
+        <v>3.92</v>
       </c>
       <c r="N97" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.65625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M98" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45954.64583333334</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="100">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="101">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="102">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="104">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="M104" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>3.53</v>
+        <v>3.75</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45954.65625</v>
+        <v>45954.70833333334</v>
       </c>
     </row>
     <row r="105">
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N106" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,7 +14124,7 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Z106" t="n">
         <v>1.8</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="107">
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45954.66666666666</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="108">
@@ -14302,27 +14302,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="109">
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="110">
@@ -14560,27 +14560,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14634,16 +14634,16 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45954.70833333334</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="112">
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.34</v>
+        <v>3.25</v>
       </c>
       <c r="M112" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N112" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.8125</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="M113" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N113" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.8125</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.89930555555</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15325,909 +15325,6 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45954.79166666666</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>B36</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Suduroy</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK116" s="3" t="n">
-        <v>45954.79166666666</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Víkingur</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" t="n">
-        <v>0</v>
-      </c>
-      <c r="W117" t="n">
-        <v>0</v>
-      </c>
-      <c r="X117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK117" s="3" t="n">
-        <v>45954.79166666666</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>B68</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK118" s="3" t="n">
-        <v>45954.79166666666</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Copiapó</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L119" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M119" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N119" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z119" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK119" s="3" t="n">
-        <v>45954.8125</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Univ. Concepción</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L120" t="n">
-        <v>2</v>
-      </c>
-      <c r="M120" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N120" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK120" s="3" t="n">
-        <v>45954.8125</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L121" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="M121" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="N121" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK121" s="3" t="n">
-        <v>45954.89930555555</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK122" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3903,52 +3903,52 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4032,52 +4032,52 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="N32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P32" t="n">
         <v>1.91</v>
       </c>
-      <c r="O32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q32" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T32" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.96</v>
+        <v>3.52</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="O33" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="R33" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T33" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.28</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.21</v>
+        <v>1.72</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="N44" t="n">
-        <v>1.99</v>
+        <v>3.67</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.31</v>
+        <v>1.93</v>
       </c>
       <c r="M51" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>1.78</v>
+        <v>3.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7809,10 +7809,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.5</v>
+        <v>1.78</v>
       </c>
       <c r="M64" t="n">
-        <v>3.91</v>
+        <v>3.53</v>
       </c>
       <c r="N64" t="n">
-        <v>1.56</v>
+        <v>3.66</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.91</v>
+        <v>4.5</v>
       </c>
       <c r="M65" t="n">
-        <v>2.95</v>
+        <v>3.91</v>
       </c>
       <c r="N65" t="n">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.78</v>
+        <v>2.91</v>
       </c>
       <c r="M66" t="n">
-        <v>3.53</v>
+        <v>2.95</v>
       </c>
       <c r="N66" t="n">
-        <v>3.66</v>
+        <v>2.29</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.69</v>
+        <v>2.19</v>
       </c>
       <c r="M68" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="N68" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N79" t="n">
-        <v>3.69</v>
+        <v>3.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="M81" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>2.88</v>
+        <v>3.69</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="M86" t="n">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="N86" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11547,7 +11547,7 @@
         <v>2.05</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="M87" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N87" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="M88" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="M89" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="N89" t="n">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,16 +11931,16 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="M91" t="n">
-        <v>3.39</v>
+        <v>2.98</v>
       </c>
       <c r="N91" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.26</v>
+        <v>2.85</v>
       </c>
       <c r="M96" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="N96" t="n">
-        <v>9.300000000000001</v>
+        <v>2.19</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13473,16 +13473,16 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G111" t="n">

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK115"/>
+  <dimension ref="A1:AK116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
         <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
         <v>2.62</v>
@@ -825,7 +825,7 @@
         <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
@@ -837,13 +837,13 @@
         <v>5.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
         <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
         <v>1.6</v>
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.41</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>1.97</v>
+        <v>3.58</v>
       </c>
       <c r="O9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4032,52 +4032,52 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="P28" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.45</v>
+        <v>7.55</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AB28" t="n">
         <v>1.28</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="M32" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="O32" t="n">
-        <v>3.88</v>
+        <v>4.3</v>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="T32" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.91</v>
       </c>
-      <c r="O33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q33" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S33" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T33" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X40" t="n">
         <v>3.85</v>
       </c>
-      <c r="N40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
       <c r="Y40" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="M44" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>3.67</v>
+        <v>2.71</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.21</v>
+        <v>2.13</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.93</v>
+        <v>3.21</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>3.25</v>
+        <v>1.99</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,16 +7545,16 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="M57" t="n">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="N57" t="n">
-        <v>2.65</v>
+        <v>3.74</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,16 +7803,16 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="M58" t="n">
-        <v>3.03</v>
+        <v>3.32</v>
       </c>
       <c r="N58" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="O58" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="M68" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>2.88</v>
+        <v>3.69</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="M69" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>3.27</v>
+        <v>4.1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="N77" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="O77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="M78" t="n">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
       <c r="N78" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="M86" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="N86" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11547,7 +11547,7 @@
         <v>2.05</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.8</v>
+        <v>2.61</v>
       </c>
       <c r="M88" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="N88" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="M89" t="n">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="N89" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11934,7 +11934,7 @@
         <v>2.05</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.68</v>
+        <v>2.35</v>
       </c>
       <c r="M90" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N90" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z90" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="M91" t="n">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z91" t="n">
         <v>2</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>1.72</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="M97" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="N97" t="n">
-        <v>4.9</v>
+        <v>3.53</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.95</v>
+        <v>2.01</v>
       </c>
       <c r="M101" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="N101" t="n">
-        <v>2.6</v>
+        <v>3.86</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13473,16 +13473,16 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45954.67708333334</v>
+        <v>45954.66666666666</v>
       </c>
     </row>
     <row r="102">
@@ -13786,27 +13786,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.02</v>
+        <v>2.95</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N104" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13860,16 +13860,16 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45954.70833333334</v>
+        <v>45954.67708333334</v>
       </c>
     </row>
     <row r="105">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="M105" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N105" t="n">
-        <v>7.3</v>
+        <v>3.75</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45954.79166666666</v>
+        <v>45954.70833333334</v>
       </c>
     </row>
     <row r="106">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45954.8125</v>
+        <v>45954.79166666666</v>
       </c>
     </row>
     <row r="113">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2</v>
+        <v>3.09</v>
       </c>
       <c r="M113" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="N113" t="n">
-        <v>3.6</v>
+        <v>2.09</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="M114" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="N114" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45954.89930555555</v>
+        <v>45954.8125</v>
       </c>
     </row>
     <row r="115">
@@ -15205,126 +15205,255 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M115" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N115" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK115" s="3" t="n">
+        <v>45954.89930555555</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>New Mexico United</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Rhode Island</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="inlineStr">
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK115" s="3" t="n">
+      <c r="L116" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N116" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="3" t="n">
         <v>45954.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -672,19 +672,19 @@
         <v>3.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="O2" t="n">
-        <v>4.77</v>
+        <v>4.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
@@ -699,31 +699,31 @@
         <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="Y2" t="n">
         <v>1.84</v>
       </c>
       <c r="Z2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.88</v>
       </c>
-      <c r="AA2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AD2" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="T8" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="U8" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>3.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.58</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.2</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.55</v>
-      </c>
       <c r="T11" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>3.76</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.31</v>
+        <v>1.89</v>
       </c>
       <c r="P27" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.54</v>
+        <v>7.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X27" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.25</v>
+        <v>2.85</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4032,52 +4032,52 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="O32" t="n">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="P32" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="R32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.36</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="Z32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="O33" t="n">
-        <v>3.88</v>
+        <v>4.3</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="R33" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="T33" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X39" t="n">
         <v>3.85</v>
       </c>
-      <c r="N39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
       <c r="Y39" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5580,52 +5580,52 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6090,58 +6090,58 @@
         <v>2.17</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N44" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="M45" t="n">
-        <v>3.17</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6483,34 +6483,34 @@
         <v>1.78</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Y47" t="n">
         <v>1.63</v>
@@ -6519,16 +6519,16 @@
         <v>2.15</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z49" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z49" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6870,34 +6870,34 @@
         <v>3.67</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y50" t="n">
         <v>1.63</v>
@@ -6906,16 +6906,16 @@
         <v>2.13</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.21</v>
+        <v>2.13</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N51" t="n">
-        <v>1.99</v>
+        <v>2.98</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="M55" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N55" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="M57" t="n">
-        <v>3.64</v>
+        <v>4.95</v>
       </c>
       <c r="N57" t="n">
-        <v>3.74</v>
+        <v>6.93</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="M58" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N58" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8676,34 +8676,34 @@
         <v>3.66</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y64" t="n">
         <v>1.67</v>
@@ -8712,16 +8712,16 @@
         <v>2.08</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8805,34 +8805,34 @@
         <v>1.56</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y65" t="n">
         <v>1.58</v>
@@ -8841,16 +8841,16 @@
         <v>2.25</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8934,34 +8934,34 @@
         <v>2.29</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y66" t="n">
         <v>2.3</v>
@@ -8970,16 +8970,16 @@
         <v>1.63</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="M67" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.85</v>
+        <v>2.73</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="N68" t="n">
-        <v>3.69</v>
+        <v>2.15</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.15</v>
+        <v>1.39</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>4.1</v>
+        <v>3.69</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="M70" t="n">
-        <v>3.99</v>
+        <v>3.92</v>
       </c>
       <c r="N70" t="n">
-        <v>4.2</v>
+        <v>2.48</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N71" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="O71" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="P71" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="R71" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S71" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="T71" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U71" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V71" t="n">
         <v>1.01</v>
       </c>
       <c r="W71" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X71" t="n">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AD71" t="n">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9828,61 +9828,61 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,61 +9957,61 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,61 +10086,61 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N75" t="n">
-        <v>3.2</v>
+        <v>5.47</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,61 +10215,61 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10353,34 +10353,34 @@
         <v>3.27</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y77" t="n">
         <v>1.82</v>
@@ -10389,16 +10389,16 @@
         <v>1.88</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="M78" t="n">
-        <v>3.16</v>
+        <v>3.65</v>
       </c>
       <c r="N78" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,61 +10602,61 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
@@ -10669,10 +10669,10 @@
         </is>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,61 +10731,61 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11127,52 +11127,52 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="M86" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N86" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.02</v>
+        <v>2.61</v>
       </c>
       <c r="M87" t="n">
-        <v>3.58</v>
+        <v>2.98</v>
       </c>
       <c r="N87" t="n">
-        <v>3.38</v>
+        <v>2.5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.61</v>
+        <v>2.02</v>
       </c>
       <c r="M88" t="n">
-        <v>2.98</v>
+        <v>3.58</v>
       </c>
       <c r="N88" t="n">
-        <v>2.5</v>
+        <v>3.38</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="M90" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="M93" t="n">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="N93" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.26</v>
+        <v>2.85</v>
       </c>
       <c r="M94" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>9.300000000000001</v>
+        <v>2.19</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.85</v>
+        <v>1.64</v>
       </c>
       <c r="M96" t="n">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="N96" t="n">
-        <v>2.19</v>
+        <v>4.9</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12933,34 +12933,34 @@
         <v>3.53</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y97" t="n">
         <v>1.95</v>
@@ -12969,16 +12969,16 @@
         <v>1.75</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>3.09</v>
+        <v>1.96</v>
       </c>
       <c r="M113" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="N113" t="n">
-        <v>2.09</v>
+        <v>3.4</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.96</v>
+        <v>3.09</v>
       </c>
       <c r="M114" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="N114" t="n">
-        <v>3.4</v>
+        <v>2.09</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>

--- a/jogos_2025-10-24.xlsx
+++ b/jogos_2025-10-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK108"/>
+  <dimension ref="A1:AK111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="N2" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="O2" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P2" t="n">
         <v>2.09</v>
@@ -687,28 +687,28 @@
         <v>2.37</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Z2" t="n">
         <v>1.86</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH2" t="n">
         <v>1.08</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O9" t="n">
-        <v>3.98</v>
+        <v>4.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.19</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="M12" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6</v>
+        <v>3.52</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.44</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.31</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>2.83</v>
+        <v>3.76</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.79</v>
+        <v>2.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3774,52 +3774,52 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.84</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,62 +4023,62 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.52</v>
+        <v>7.84</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="T28" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="U28" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.64</v>
       </c>
-      <c r="AD28" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.25</v>
+        <v>2.85</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="O30" t="n">
         <v>2.83</v>
@@ -4296,7 +4296,7 @@
         <v>1.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="R30" t="n">
         <v>1.52</v>
@@ -4314,10 +4314,10 @@
         <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="X30" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="Y30" t="n">
         <v>2.51</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5193,52 +5193,52 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O38" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.36</v>
+        <v>4.15</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="T38" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="U38" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X38" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="O39" t="n">
-        <v>1.71</v>
+        <v>4.2</v>
       </c>
       <c r="P39" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.550000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="R39" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S39" t="n">
-        <v>3.22</v>
+        <v>3.06</v>
       </c>
       <c r="T39" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="U39" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AH39" t="n">
-        <v>3.42</v>
+        <v>1.24</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="M40" t="n">
-        <v>3.41</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>3.61</v>
+        <v>7.6</v>
       </c>
       <c r="O40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P40" t="n">
         <v>2.47</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q40" t="n">
-        <v>4.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="T40" t="n">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X40" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.85</v>
+        <v>3.42</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.13</v>
+        <v>3.31</v>
       </c>
       <c r="M41" t="n">
-        <v>3.17</v>
+        <v>3.89</v>
       </c>
       <c r="N41" t="n">
-        <v>2.98</v>
+        <v>1.78</v>
       </c>
       <c r="O41" t="n">
-        <v>2.95</v>
+        <v>4.08</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S41" t="n">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="U41" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
         <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.51</v>
+        <v>1.16</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="N42" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="O42" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="T42" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="U42" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X42" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>1.26</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.72</v>
+        <v>3.21</v>
       </c>
       <c r="M44" t="n">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>3.67</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
-        <v>2.17</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>2.49</v>
+        <v>2.07</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.55</v>
+        <v>2.58</v>
       </c>
       <c r="R44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.25</v>
       </c>
-      <c r="S44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC44" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH44" t="n">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.31</v>
+        <v>4.4</v>
       </c>
       <c r="M46" t="n">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="O46" t="n">
-        <v>4.08</v>
+        <v>4.19</v>
       </c>
       <c r="P46" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="T46" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="U46" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X46" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.62</v>
+        <v>3.42</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH46" t="n">
         <v>1.16</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,77 +6603,77 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="O48" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z48" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="AA48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH48" t="n">
         <v>1.41</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.4</v>
+        <v>1.93</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
-        <v>4.19</v>
+        <v>2.55</v>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="R50" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S50" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="U50" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="X50" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.16</v>
+        <v>1.73</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S52" t="n">
         <v>3.5</v>
       </c>
-      <c r="N52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T52" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="U52" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X52" t="n">
-        <v>4.42</v>
+        <v>5.13</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="M53" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="N53" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="O53" t="n">
         <v>3.82</v>
@@ -7281,10 +7281,10 @@
         <v>1.03</v>
       </c>
       <c r="W53" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X53" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="Y53" t="n">
         <v>2.37</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.27</v>
+        <v>1.96</v>
       </c>
       <c r="M55" t="n">
-        <v>3.32</v>
+        <v>3.66</v>
       </c>
       <c r="N55" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="O55" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="P55" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="